--- a/AAII_Financials/Quarterly/ALL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
   <si>
     <t>ALL</t>
   </si>
@@ -656,521 +656,533 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>18596000</v>
+      </c>
+      <c r="E8" s="3">
         <v>16941000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>17345000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>17255000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>16633000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>16452000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>16506000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>16627000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>15714000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15259000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14832000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>14497000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>13979000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>13786000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13648000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>13208000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>12219000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>12336000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>13011000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>12480000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>12646000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>12451000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10962000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10678000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>10403000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>9866000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>11476000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>11085000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>11156000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>11006000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>9486000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>10469000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>10103000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>9770000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>9854000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>9686000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>9634000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>9496000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>9350000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>9294000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>12136000</v>
+      </c>
+      <c r="E9" s="3">
         <v>11439000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9929000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10822000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12513000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>13235000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>11423000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12763000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13093000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>11736000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10970000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12340000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>13774000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12335000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1725000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1683000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1618000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1608000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1602000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1582000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1545000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1523000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1382000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1386000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1344000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1365000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1382000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1425000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1362000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1364000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1336000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1317000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1296000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1273000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1239000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1200000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1176000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1169000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1157000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1138000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>6460000</v>
+      </c>
+      <c r="E10" s="3">
         <v>5502000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7416000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6433000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4120000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3217000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5083000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3864000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2621000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3523000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3862000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2157000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>205000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1451000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>11923000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>11525000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>10601000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>10728000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>11409000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>10898000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>11101000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>10928000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>9580000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>9292000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>9059000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8501000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>10094000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>9660000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>9794000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>9642000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>8150000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>9152000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>8807000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>8497000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>8615000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>8486000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>8458000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>8327000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>8193000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>8156000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1213,8 +1225,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1335,8 +1348,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1457,213 +1473,219 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E14" s="3">
         <v>5000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>20000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-703000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-875000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>16000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>10000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>28000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>13000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>10000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>28000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>87000</v>
-      </c>
-      <c r="O14" s="3">
-        <v>27000</v>
       </c>
       <c r="P14" s="3">
         <v>27000</v>
       </c>
       <c r="Q14" s="3">
+        <v>27000</v>
+      </c>
+      <c r="R14" s="3">
         <v>24000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>14000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>12000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>25000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>23000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>100000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>73000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>39000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>195000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>750000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>213000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>66000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>16000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>74000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>33000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>15000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>16000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>25000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>18000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>163000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>39000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>88000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>70000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>80000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>77000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E15" s="3">
         <v>47000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>56000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>59000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>57000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>59000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>70000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>71000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>70000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>69000</v>
-      </c>
-      <c r="M15" s="3">
-        <v>83000</v>
       </c>
       <c r="N15" s="3">
         <v>83000</v>
       </c>
       <c r="O15" s="3">
+        <v>83000</v>
+      </c>
+      <c r="P15" s="3">
         <v>82000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>81000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>89000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>90000</v>
-      </c>
-      <c r="S15" s="3">
-        <v>87000</v>
       </c>
       <c r="T15" s="3">
         <v>87000</v>
       </c>
       <c r="U15" s="3">
-        <v>109000</v>
+        <v>87000</v>
       </c>
       <c r="V15" s="3">
         <v>109000</v>
       </c>
       <c r="W15" s="3">
+        <v>109000</v>
+      </c>
+      <c r="X15" s="3">
         <v>105000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>53000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>30000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>31000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>29000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>28000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>30000</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>32000</v>
       </c>
       <c r="AE15" s="3">
         <v>32000</v>
@@ -1672,28 +1694,28 @@
         <v>32000</v>
       </c>
       <c r="AG15" s="3">
+        <v>32000</v>
+      </c>
+      <c r="AH15" s="3">
         <v>36000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>24000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>23000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>22000</v>
       </c>
-      <c r="AK15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL15" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AM15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN15" s="3">
-        <v>0</v>
+      <c r="AN15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AO15" s="3">
         <v>0</v>
@@ -1701,8 +1723,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1742,252 +1767,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14351000</v>
+      </c>
+      <c r="E17" s="3">
         <v>13730000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>12312000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13038000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14705000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>15617000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13946000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15077000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15173000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13688000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12870000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14343000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15602000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14079000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14058000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14118000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>13530000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>11535000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>11618000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>12254000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10849000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9419000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8098000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9150000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9024000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8835000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9245000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9925000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>10078000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>9386000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>10196000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>9291000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>9206000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>8507000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>8697000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>8715000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>8783000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>8484000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>8092000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>8529000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4245000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3211000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5033000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4217000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1928000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>835000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2560000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1550000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>541000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1571000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1962000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>154000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1623000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-293000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-410000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-910000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1311000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>801000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1393000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>226000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1797000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3032000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2864000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1528000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1379000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1031000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2231000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1160000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1078000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1620000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-710000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1178000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>897000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1263000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1157000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>971000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>851000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1012000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>1258000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2030,8 +2062,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2074,8 +2107,8 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -2152,175 +2185,181 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4291000</v>
+      </c>
+      <c r="E21" s="3">
         <v>3258000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5089000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4276000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1985000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>894000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2630000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1621000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>611000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1640000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2045000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>237000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1541000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-212000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-209000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-716000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1095000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1037000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1661000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>473000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2108000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3292000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>3050000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1710000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1542000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1186000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2402000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1319000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1238000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1777000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-575000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1306000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1023000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1385000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1282000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1091000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>970000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1131000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1355000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>862000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>98000</v>
+        <v>96000</v>
       </c>
       <c r="E22" s="3">
         <v>98000</v>
       </c>
       <c r="F22" s="3">
+        <v>98000</v>
+      </c>
+      <c r="G22" s="3">
         <v>101000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>100000</v>
       </c>
       <c r="H22" s="3">
         <v>100000</v>
       </c>
       <c r="I22" s="3">
+        <v>100000</v>
+      </c>
+      <c r="J22" s="3">
         <v>101000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>104000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>98000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>97000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>107000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>88000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>98000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>86000</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -2396,252 +2435,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4142000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3108000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4915000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4819000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2703000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>719000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2449000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1418000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>430000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1464000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1827000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-21000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1748000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-406000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-410000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-910000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1311000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>801000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1393000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>226000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1797000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3032000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2864000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1528000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1379000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1031000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2231000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1160000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1078000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1620000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-710000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1178000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>897000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1263000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1157000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>971000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>851000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1012000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>1258000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>765000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>871000</v>
+      </c>
+      <c r="E24" s="3">
         <v>650000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1088000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1075000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>604000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>123000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>559000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>254000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>83000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>266000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>340000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-17000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-373000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-85000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-114000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-236000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-289000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>151000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>281000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>20000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>362000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>626000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>594000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>312000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>273000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>194000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>458000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>229000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>227000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>328000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-170000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>230000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>180000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>257000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>414000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>305000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>272000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>317000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>418000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>245000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2762,252 +2810,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3271000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2458000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3827000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3744000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2099000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>596000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1890000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1164000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>347000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1198000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1487000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1375000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-321000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-296000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-674000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1022000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>650000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1112000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>206000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1435000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2406000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2270000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1216000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1106000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>837000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1773000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>931000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>851000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1292000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-540000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>948000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>717000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1006000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>743000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>666000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>579000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>695000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>840000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>520000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3241000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2428000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3803000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3717000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2079000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>566000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1899000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1161000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>301000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1189000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1460000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-41000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1389000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-346000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-303000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-685000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1040000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>634000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1111000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>183000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1399000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2385000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2244000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1189000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1080000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>801000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1707000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>889000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>821000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1261000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-583000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>911000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>678000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>977000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>714000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>637000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>550000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>666000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>811000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3128,8 +3185,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3172,11 +3232,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -3185,32 +3245,32 @@
         <v>0</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>-321000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>325000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>196000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-3793000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>354000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-63000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>144000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-288000</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3220,24 +3280,24 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>31000</v>
       </c>
-      <c r="AI29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>506000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3250,8 +3310,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3372,8 +3435,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3494,8 +3560,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3538,8 +3607,8 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -3616,130 +3685,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3271000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2457000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3832000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3746000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2109000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>595000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1928000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1190000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>331000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1218000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1489000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1352000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-320000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-303000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-685000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1040000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>634000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>790000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>508000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1595000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1408000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2598000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1126000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1224000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>513000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1707000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>889000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>821000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1261000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-585000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>942000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>678000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>977000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1220000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>637000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>550000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>666000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>811000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3860,257 +3935,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3271000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2457000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3832000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3746000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2109000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>595000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1928000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1190000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>331000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1218000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1489000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1352000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-320000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-303000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-685000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1040000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>634000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>790000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>508000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1595000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1408000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2598000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1126000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1224000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>513000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1707000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>889000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>821000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1261000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-585000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>942000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>678000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>977000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1220000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>637000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>550000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>666000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>811000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4153,8 +4237,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4197,175 +4282,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>840000</v>
+      </c>
+      <c r="E41" s="3">
         <v>697000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>678000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>931000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>995000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>840000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>704000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>816000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>599000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>850000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>722000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>860000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>699000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>662000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>736000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>786000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>766000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1130000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>763000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>690000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>656000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>709000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>377000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>370000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>547000</v>
-      </c>
-      <c r="AB41" s="3">
-        <v>338000</v>
       </c>
       <c r="AC41" s="3">
         <v>338000</v>
       </c>
       <c r="AD41" s="3">
+        <v>338000</v>
+      </c>
+      <c r="AE41" s="3">
         <v>587000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>599000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>551000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>499000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>460000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>489000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>450000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>617000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>690000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>482000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>442000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>436000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>389000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4875000</v>
+      </c>
+      <c r="E42" s="3">
         <v>4705000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4887000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>8743000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>9640000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6541000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4537000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>6995000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5289000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4319000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>5146000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3369000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>5137000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>6724000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4441,130 +4530,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11864000</v>
+      </c>
+      <c r="E43" s="3">
         <v>11648000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>11474000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11745000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>11271000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11053000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10614000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11041000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10762000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10573000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10044000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10102000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9713000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9483000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9165000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>9150000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>8824000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>8874000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>8364000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>8406000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>8146000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>7921000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6479000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6609000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>6367000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>6401000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>6472000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>6558000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>6380000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>6201000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>6154000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>6196000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>5953000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>5856000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>5786000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>5922000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>5693000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>5649000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>5597000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>5799000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4607,8 +4702,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4685,53 +4780,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8742000</v>
+      </c>
+      <c r="E45" s="3">
         <v>9216000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>9356000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>10277000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11126000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>14627000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>12765000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>12904000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9461000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9416000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9472000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>9731000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9728000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>10088000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4807,53 +4905,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>26321000</v>
+      </c>
+      <c r="E46" s="3">
         <v>26266000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>26395000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>31696000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>33032000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>33061000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>28620000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>31756000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>26111000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>25158000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>25384000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>24062000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>25277000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>26957000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4929,320 +5030,329 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>80949000</v>
+      </c>
+      <c r="E47" s="3">
         <v>78445000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>76368000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>71750000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>66027000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>65840000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>66468000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>64978000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>63524000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>61724000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>59659000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>57656000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>56095000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>54354000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>61829000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>61006000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>61055000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>61768000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>64701000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>61840000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>62570000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>60076000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>94237000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>91197000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>89637000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>84783000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>88221000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>89158000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>86345000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>84018000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>81136000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>83855000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>83140000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>83195000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>82677000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>82680000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>81203000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>81050000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>81707000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>81038000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>591000</v>
+      </c>
+      <c r="E48" s="3">
         <v>606000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>781000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>601000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>619000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>632000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>834000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>714000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>777000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>802000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1022000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>909000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>945000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>971000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1221000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1008000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>975000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>966000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1253000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>965000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1026000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1002000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1057000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1076000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1100000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1123000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1628000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1535000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1519000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1521000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1045000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1032000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1040000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1060000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1072000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1067000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1072000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1067000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>1065000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>1013000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9257000</v>
+      </c>
+      <c r="E49" s="3">
         <v>9188000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9839000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9213000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9048000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8902000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9772000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8957000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9614000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9448000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10408000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9326000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9109000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8973000</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>3502000</v>
       </c>
       <c r="R49" s="3">
         <v>3502000</v>
       </c>
       <c r="S49" s="3">
+        <v>3502000</v>
+      </c>
+      <c r="T49" s="3">
         <v>3496000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3497000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3502000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3389000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3349000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3350000</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>2544000</v>
       </c>
       <c r="Z49" s="3">
         <v>2544000</v>
@@ -5254,22 +5364,22 @@
         <v>2544000</v>
       </c>
       <c r="AC49" s="3">
-        <v>2545000</v>
+        <v>2544000</v>
       </c>
       <c r="AD49" s="3">
         <v>2545000</v>
       </c>
       <c r="AE49" s="3">
-        <v>2547000</v>
+        <v>2545000</v>
       </c>
       <c r="AF49" s="3">
         <v>2547000</v>
       </c>
       <c r="AG49" s="3">
+        <v>2547000</v>
+      </c>
+      <c r="AH49" s="3">
         <v>2530000</v>
-      </c>
-      <c r="AH49" s="3">
-        <v>2189000</v>
       </c>
       <c r="AI49" s="3">
         <v>2189000</v>
@@ -5278,25 +5388,28 @@
         <v>2189000</v>
       </c>
       <c r="AK49" s="3">
+        <v>2189000</v>
+      </c>
+      <c r="AL49" s="3">
         <v>2181000</v>
-      </c>
-      <c r="AL49" s="3">
-        <v>2309000</v>
       </c>
       <c r="AM49" s="3">
         <v>2309000</v>
       </c>
       <c r="AN49" s="3">
+        <v>2309000</v>
+      </c>
+      <c r="AO49" s="3">
         <v>2295000</v>
-      </c>
-      <c r="AO49" s="3">
-        <v>1219000</v>
       </c>
       <c r="AP49" s="3">
         <v>1219000</v>
       </c>
+      <c r="AQ49" s="3">
+        <v>1219000</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5417,8 +5530,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5539,77 +5655,80 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6232000</v>
+      </c>
+      <c r="E52" s="3">
         <v>8067000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5023000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5928000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5909000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5453000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4707000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6386000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7046000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6849000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5505000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6776000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6997000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6432000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>382000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>492000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>118000</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3">
         <v>36803000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>36969000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>36829000</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>8</v>
       </c>
@@ -5625,8 +5744,8 @@
       <c r="AD52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE52" s="3">
-        <v>0</v>
+      <c r="AE52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF52" s="3">
         <v>0</v>
@@ -5661,8 +5780,11 @@
       <c r="AP52" s="3">
         <v>0</v>
       </c>
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5783,130 +5905,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>124756000</v>
+      </c>
+      <c r="E54" s="3">
         <v>123972000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>119758000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>120402000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>115894000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>115161000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>111617000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>113743000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>108368000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>105241000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>103362000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>101176000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>100514000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>99631000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>97989000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>97676000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>96350000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>97150000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>99440000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>133440000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>132643000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>129811000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>125987000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>122750000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>121266000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>116107000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>119950000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>121073000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>118374000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>115834000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>112249000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>114490000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>113369000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>113289000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>112422000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>113632000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>110865000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>110243000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>108610000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>108537000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5949,8 +6077,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5993,53 +6122,54 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>42531000</v>
+      </c>
+      <c r="E57" s="3">
         <v>42793000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>42498000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>44657000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>45796000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>45494000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>43484000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>44470000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>43128000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>41634000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>41211000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>42139000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>41918000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>39977000</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -6115,53 +6245,56 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>551000</v>
+        <v>555000</v>
       </c>
       <c r="E58" s="3">
+        <v>552000</v>
+      </c>
+      <c r="F58" s="3">
         <v>618000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>601000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>604000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>601000</v>
       </c>
       <c r="I58" s="3">
         <v>601000</v>
       </c>
       <c r="J58" s="3">
+        <v>601000</v>
+      </c>
+      <c r="K58" s="3">
         <v>9000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>2000</v>
       </c>
       <c r="L58" s="3">
         <v>2000</v>
       </c>
       <c r="M58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N58" s="3">
         <v>351000</v>
-      </c>
-      <c r="N58" s="3">
-        <v>2000</v>
       </c>
       <c r="O58" s="3">
         <v>2000</v>
       </c>
       <c r="P58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Q58" s="3">
         <v>3000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6237,175 +6370,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>28865000</v>
+        <v>29393000</v>
       </c>
       <c r="E59" s="3">
+        <v>28867000</v>
+      </c>
+      <c r="F59" s="3">
         <v>29085000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>29186000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>28047000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>29543000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>29022000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>29230000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>25932000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>24945000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>24714000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>24527000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>23380000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>22502000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>24843000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>24211000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>23229000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>22429000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>22490000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>21753000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>20853000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>20274000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>49274000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>49140000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>48221000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>46664000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>48503000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>48555000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>48232000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>48055000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>47670000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>48313000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>47936000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>47972000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>48614000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>48542000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>48216000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>48129000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>48185000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>48745000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>72209000</v>
+        <v>72479000</v>
       </c>
       <c r="E60" s="3">
+        <v>72212000</v>
+      </c>
+      <c r="F60" s="3">
         <v>72201000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>74444000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>74447000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>75638000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>73107000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>73709000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>69062000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>66581000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>66276000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>66668000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>65300000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>62482000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6481,175 +6620,181 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6942000</v>
+      </c>
+      <c r="E61" s="3">
         <v>6941000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7057000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7489000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7487000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7486000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7720000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8083000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8082000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7938000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7857000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7946000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7949000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8452000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7964000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7967000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7970000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7973000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7976000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7980000</v>
-      </c>
-      <c r="W61" s="3">
-        <v>7996000</v>
       </c>
       <c r="X61" s="3">
         <v>7996000</v>
       </c>
       <c r="Y61" s="3">
+        <v>7996000</v>
+      </c>
+      <c r="Z61" s="3">
         <v>7825000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6635000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6634000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6633000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6631000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6630000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6628000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>6453000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>6451000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>6450000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>6448000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>6847000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>6350000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>6349000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>6348000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>6346000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>6347000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>5110000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>13235000</v>
+        <v>11485000</v>
       </c>
       <c r="E62" s="3">
+        <v>13232000</v>
+      </c>
+      <c r="F62" s="3">
         <v>9511000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10669000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9955000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9985000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9187000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10902000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>12651000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>12242000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>11270000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>12115000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>11893000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>11324000</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6657,76 +6802,79 @@
         <v>0</v>
       </c>
       <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
         <v>402000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>833000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>33132000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>33533000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>33876000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1355000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>905000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>842000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>331000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1154000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1079000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>997000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>817000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>425000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>660000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>723000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>725000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>782000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1249000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1104000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>833000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>487000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>935000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6847,8 +6995,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6969,8 +7120,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7091,130 +7245,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>91078000</v>
+      </c>
+      <c r="E66" s="3">
         <v>92385000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>89169000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>92913000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>91889000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>93109000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>90250000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>92905000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>89795000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>86761000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>85732000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>86729000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>85142000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>82258000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>80501000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>80003000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>76235000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>73938000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>74261000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>106711000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>104436000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>102992000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>95770000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>95487000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>94280000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>91934000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>93952000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>94933000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>93898000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>92416000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>90937000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>90857000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>90247000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>90012000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>89871000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>91513000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>89364000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>89085000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>88037000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>87603000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7257,8 +7417,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7379,8 +7540,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7501,8 +7665,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7543,7 +7710,7 @@
         <v>2001000</v>
       </c>
       <c r="P70" s="3">
-        <v>1970000</v>
+        <v>2001000</v>
       </c>
       <c r="Q70" s="3">
         <v>1970000</v>
@@ -7564,13 +7731,13 @@
         <v>1970000</v>
       </c>
       <c r="W70" s="3">
-        <v>2170000</v>
+        <v>1970000</v>
       </c>
       <c r="X70" s="3">
         <v>2170000</v>
       </c>
       <c r="Y70" s="3">
-        <v>1970000</v>
+        <v>2170000</v>
       </c>
       <c r="Z70" s="3">
         <v>1970000</v>
@@ -7582,13 +7749,13 @@
         <v>1970000</v>
       </c>
       <c r="AC70" s="3">
+        <v>1970000</v>
+      </c>
+      <c r="AD70" s="3">
         <v>2248000</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>3052000</v>
-      </c>
-      <c r="AE70" s="3">
-        <v>1930000</v>
       </c>
       <c r="AF70" s="3">
         <v>1930000</v>
@@ -7597,7 +7764,7 @@
         <v>1930000</v>
       </c>
       <c r="AH70" s="3">
-        <v>2303000</v>
+        <v>1930000</v>
       </c>
       <c r="AI70" s="3">
         <v>2303000</v>
@@ -7606,7 +7773,7 @@
         <v>2303000</v>
       </c>
       <c r="AK70" s="3">
-        <v>1746000</v>
+        <v>2303000</v>
       </c>
       <c r="AL70" s="3">
         <v>1746000</v>
@@ -7623,8 +7790,11 @@
       <c r="AP70" s="3">
         <v>1746000</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>1746000</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7745,130 +7915,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>67504000</v>
+      </c>
+      <c r="E72" s="3">
         <v>64540000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>62393000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>58853000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>55400000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>53586000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>53288000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>51635000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>50718000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>50662000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>49716000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>48491000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>48766000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>50388000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>50970000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>51490000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>52412000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>53688000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>53294000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>52736000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>52464000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>51107000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>52767000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>50336000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>49380000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>48326000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>48074000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>46527000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>45803000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>45148000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>45708000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>46178000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>45508000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>45031000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>43162000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>42125000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>41622000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>41208000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>40678000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>39990000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7989,8 +8165,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8111,8 +8290,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8233,130 +8415,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>31697000</v>
+      </c>
+      <c r="E76" s="3">
         <v>29606000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>28609000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>25504000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22018000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20054000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19441000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18876000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16592000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16638000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15769000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12592000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13516000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15524000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15518000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>15703000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>18145000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>21242000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>23209000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>24759000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>26037000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>24649000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>28247000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>25293000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>25016000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>22203000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>23750000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>23088000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>22546000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>21488000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>19382000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>21330000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>20819000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>20974000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>20805000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>20373000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>19755000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>19412000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>18827000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>19188000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8477,257 +8665,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3271000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2457000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3832000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3746000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2109000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>595000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1928000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1190000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>331000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1218000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1489000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1352000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-320000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-303000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-685000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1040000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>634000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>790000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>508000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1595000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1408000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2598000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1126000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1224000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>513000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1707000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>889000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>821000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1261000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-585000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>942000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>678000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>977000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1220000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>637000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>550000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>666000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>811000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>491000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8770,130 +8967,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E83" s="3">
         <v>73000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>81000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>69000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>62000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>63000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>82000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>93000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>104000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>96000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>112000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>104000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>129000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>149000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>201000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>194000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>216000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>236000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>268000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>247000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>311000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>260000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>186000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>182000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>163000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>155000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>171000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>159000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>160000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>157000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>135000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>128000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>126000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>122000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>125000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>120000</v>
-      </c>
-      <c r="AM83" s="3">
-        <v>119000</v>
       </c>
       <c r="AN83" s="3">
         <v>119000</v>
       </c>
       <c r="AO83" s="3">
-        <v>97000</v>
+        <v>119000</v>
       </c>
       <c r="AP83" s="3">
         <v>97000</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>97000</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9014,8 +9215,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9136,8 +9340,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9258,8 +9465,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9380,8 +9590,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9502,130 +9715,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2634000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3562000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2989000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3284000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1873000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1964000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1705000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3201000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2359000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1666000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1225000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1233000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1169000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>601000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>970000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2046000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1673000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>432000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>871000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1329000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1551000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1365000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1319000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1296000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1849000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1027000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1234000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1833000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1348000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>714000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1357000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1728000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1464000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>626000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1100000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1866000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>491000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>857000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1251000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>1384000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9668,130 +9887,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-40000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-89000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-48000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>1000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-92000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-50000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-63000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-56000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-41000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-71000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-55000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-62000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-79000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-68000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-124000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-98000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-130000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-59000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-89000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-136000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-61000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-73000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-69000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-101000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-65000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-140000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-120000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-93000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-80000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-82000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-67000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-66000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-62000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-83000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-70000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-72000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-74000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-123000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9912,8 +10135,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10034,130 +10260,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1161000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2627000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1949000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2805000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1208000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1293000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1671000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2685000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2524000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1372000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1105000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-845000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-253000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-796000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-447000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1143000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1119000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>981000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>221000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>446000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-670000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>513000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2198000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-285000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1026000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>68000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>428000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2093000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-879000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-263000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>737000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1145000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-60000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1251000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-140000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1127000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>337000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-280000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-1868000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-834000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10200,28 +10432,29 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>280000</v>
+      </c>
+      <c r="E96" s="3">
         <v>261000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>263000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>264000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>265000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>244000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>243000</v>
       </c>
       <c r="J96" s="3">
         <v>243000</v>
@@ -10230,7 +10463,7 @@
         <v>243000</v>
       </c>
       <c r="L96" s="3">
-        <v>233000</v>
+        <v>243000</v>
       </c>
       <c r="M96" s="3">
         <v>233000</v>
@@ -10239,91 +10472,94 @@
         <v>233000</v>
       </c>
       <c r="O96" s="3">
+        <v>233000</v>
+      </c>
+      <c r="P96" s="3">
         <v>235000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>224000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-228000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-232000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-236000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-230000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-235000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-241000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-245000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-164000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-168000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-169000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-172000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-159000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-163000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-166000</v>
       </c>
       <c r="AE96" s="3">
         <v>-166000</v>
       </c>
       <c r="AF96" s="3">
+        <v>-166000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-158000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-159000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-160000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-163000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-132000</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>-134000</v>
       </c>
       <c r="AL96" s="3">
         <v>-134000</v>
       </c>
       <c r="AM96" s="3">
+        <v>-134000</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-135000</v>
-      </c>
-      <c r="AN96" s="3">
-        <v>-122000</v>
       </c>
       <c r="AO96" s="3">
         <v>-122000</v>
       </c>
       <c r="AP96" s="3">
+        <v>-122000</v>
+      </c>
+      <c r="AQ96" s="3">
         <v>-124000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10444,8 +10680,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10566,8 +10805,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10688,130 +10930,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1330000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-916000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1293000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-634000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-620000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-334000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-260000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-185000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-86000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-166000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-258000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-227000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-879000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>121000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-573000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-883000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-918000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1046000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1175000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1743000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-842000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1480000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>886000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1188000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-614000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1095000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1911000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>248000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-421000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-399000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2055000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-612000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1365000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>458000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1033000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-531000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-788000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-571000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>664000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-607000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10854,8 +11102,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10932,126 +11180,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>143000</v>
+      </c>
+      <c r="E102" s="3">
         <v>19000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-253000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-155000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>45000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>337000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-226000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>331000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-251000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>128000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-138000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>161000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>37000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-74000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-50000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>20000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-364000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>367000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-83000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>32000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>39000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>398000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>7000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-177000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>209000</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
-      </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-249000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-12000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>48000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>52000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>39000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-29000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>39000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-167000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-73000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>208000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>40000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>6000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>47000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-57000</v>
       </c>
     </row>
